--- a/data/trans_bre/KIDM_A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_A_R-Edad-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -612,42 +612,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2,54</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,81</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-51,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-53,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-34,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,64; 1,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,27; 1,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,72; 1,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,72; 6,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 267,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-91,02; 62,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-92,38; 224,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>12-15</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -712,42 +712,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,45</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>122,15%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-73,96%</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,58; 3,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,66; 4,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,9; 2,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,07; 0,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-54,18; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-50,21; 346,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8-11</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -812,42 +812,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-1,5</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-2,54</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,81</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-51,99%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-53,99%</t>
+          <t>-12,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>-34,87%</t>
+          <t>-8,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>-4,03%</t>
         </is>
       </c>
     </row>
@@ -860,262 +860,60 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 1,59</t>
+          <t>-1,41; 2,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 0,84</t>
+          <t>-2,99; 1,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 1,49</t>
+          <t>-1,84; 1,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 6,66</t>
+          <t>-1,92; 1,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 433,36</t>
+          <t>-59,43; 223,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-89,91; 53,1</t>
+          <t>-62,01; 72,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-90,91; 201,13</t>
+          <t>-74,28; 166,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,67; 389,1</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,44</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,54</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,83</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>122,15%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>53,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-73,96%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,8; 3,77</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,57; 4,96</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,85; 2,54</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,3; 0,27</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-57,24; 944,72</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-43,24; 345,82</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-12,29%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-8,41%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-4,03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,57; 2,44</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,83; 1,94</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,87; 1,49</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,09; 1,71</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-62,28; 238,28</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-58,81; 83,02</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-71,16; 184,35</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 318,49</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="6">
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_bre/KIDM_A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_A_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 1,43</t>
+          <t>-4,85; 1,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 1,07</t>
+          <t>-6,18; 0,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 1,49</t>
+          <t>-3,61; 1,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 6,8</t>
+          <t>-1,58; 6,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 267,71</t>
+          <t>-100,0; 260,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-91,02; 62,96</t>
+          <t>-89,71; 55,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-92,38; 224,88</t>
+          <t>-89,3; 211,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,95</t>
+          <t>-0,51; 4,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 4,82</t>
+          <t>-1,19; 4,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 2,54</t>
+          <t>-1,67; 2,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,25</t>
+          <t>-3,52; 0,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,18; —</t>
+          <t>-53,52; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,21; 346,33</t>
+          <t>-42,12; 369,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,33</t>
+          <t>-1,47; 2,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,87</t>
+          <t>-2,68; 2,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,36</t>
+          <t>-1,87; 1,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,75</t>
+          <t>-1,76; 1,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-59,43; 223,72</t>
+          <t>-58,76; 232,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-62,01; 72,51</t>
+          <t>-57,28; 84,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-74,28; 166,76</t>
+          <t>-74,95; 162,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-90,67; 389,1</t>
+          <t>-94,52; 466,48</t>
         </is>
       </c>
     </row>
